--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.144.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.144.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -879,7 +879,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.144.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.144.xlsx
@@ -423,15 +423,15 @@
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="41" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.144.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.144.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0144.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0144.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
@@ -603,18 +603,18 @@
       <c r="G2" s="1" t="inlineStr"/>
       <c r="H2" s="1" t="inlineStr"/>
       <c r="I2" s="1" t="inlineStr"/>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>L20: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: (Pray subpenaÃ¦na.)</t>
-        </is>
-      </c>
+      <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L10: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: f the will â€¢</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]A</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]A</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L8: isolated marker/symbol line :: A</t>
@@ -622,19 +622,19 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L5: isolated marker/symbol line :: 137</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]A</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
       <c r="Q2" s="1" t="inlineStr">
         <is>
-          <t>L45: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: --------day of ------â€” your orator entered into an the vendor,</t>
+          <t>L45: punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: --------day of ------— your orator entered into an the vendor,</t>
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
       <c r="S2" s="1" t="inlineStr">
         <is>
-          <t>L45: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: --------day of ------â€” your orator entered into an the vendor,</t>
+          <t>L45: punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: --------day of ------— your orator entered into an the vendor,</t>
         </is>
       </c>
       <c r="T2" s="1" t="inlineStr"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>96</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -674,14 +674,10 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L33: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: -at or for the price or sum of Â£â€”â€” Â£â€”â€” Â£â€”</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L32: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: Ã¨removed and applied to his own use aforesaid, and that</t>
+          <t>L10: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: f the will •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -693,7 +689,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L92: isolated marker/symbol line :: :</t>
+          <t>L5: isolated marker/symbol line :: 137</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -705,7 +701,7 @@
       <c r="R3" s="1" t="inlineStr"/>
       <c r="S3" s="1" t="inlineStr">
         <is>
-          <t>L103: punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: -----and</t>
+          <t>L66: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • doned the same and departed this Province, and has re-</t>
         </is>
       </c>
       <c r="T3" s="1" t="inlineStr"/>
@@ -737,14 +733,10 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L104: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: (And for further relief ; pray subpenaÃ¦na.)</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L36: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: (Pray subpÅ“na.) rÃ©.</t>
+          <t>L66: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • doned the same and departed this Province, and has re-</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -756,17 +748,21 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L94: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: â€”</t>
+          <t>L92: isolated marker/symbol line :: :</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr">
         <is>
-          <t>L49: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€” concession of the township of â€”- ----in the</t>
+          <t>L49: punctuation artifact: double/multiple hyphen :: — concession of the township of —- ----in the</t>
         </is>
       </c>
       <c r="R4" s="1" t="inlineStr"/>
-      <c r="S4" s="1" t="inlineStr"/>
+      <c r="S4" s="1" t="inlineStr">
+        <is>
+          <t>L103: punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: -----and</t>
+        </is>
+      </c>
       <c r="T4" s="1" t="inlineStr"/>
       <c r="U4" s="1" t="inlineStr"/>
       <c r="V4" s="1" t="inlineStr"/>
@@ -782,12 +778,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -797,11 +793,7 @@
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr"/>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L45: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: --------day of ------â€” your orator entered into an the vendor,</t>
-        </is>
-      </c>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
@@ -809,11 +801,15 @@
           <t>L38: isolated marker/symbol line :: 137</t>
         </is>
       </c>
-      <c r="O5" s="1" t="inlineStr"/>
+      <c r="O5" s="1" t="inlineStr">
+        <is>
+          <t>L94: isolated marker/symbol line :: —</t>
+        </is>
+      </c>
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr">
         <is>
-          <t>L50: punctuation artifact: double/multiple hyphen :: county of ------at or for the price or sum of Â£-</t>
+          <t>L50: punctuation artifact: double/multiple hyphen :: county of ------at or for the price or sum of £-</t>
         </is>
       </c>
       <c r="R5" s="1" t="inlineStr"/>
@@ -848,11 +844,7 @@
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
       <c r="J6" s="1" t="inlineStr"/>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L49: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€” concession of the township of â€”- ----in the</t>
-        </is>
-      </c>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
@@ -864,7 +856,7 @@
       <c r="P6" s="1" t="inlineStr"/>
       <c r="Q6" s="1" t="inlineStr">
         <is>
-          <t>L52: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€” payable by ---------equal annual instalments with</t>
+          <t>L52: punctuation artifact: double/multiple hyphen :: — payable by ---------equal annual instalments with</t>
         </is>
       </c>
       <c r="R6" s="1" t="inlineStr"/>
@@ -899,11 +891,7 @@
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
       <c r="J7" s="1" t="inlineStr"/>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L52: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€” payable by ---------equal annual instalments with</t>
-        </is>
-      </c>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
@@ -915,7 +903,7 @@
       <c r="P7" s="1" t="inlineStr"/>
       <c r="Q7" s="1" t="inlineStr">
         <is>
-          <t>L69: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: Â£â€” which he paid on the â€” --------day of ------</t>
+          <t>L69: punctuation artifact: double/multiple hyphen :: £— which he paid on the — --------day of ------</t>
         </is>
       </c>
       <c r="R7" s="1" t="inlineStr"/>
@@ -950,11 +938,7 @@
       <c r="H8" s="1" t="inlineStr"/>
       <c r="I8" s="1" t="inlineStr"/>
       <c r="J8" s="1" t="inlineStr"/>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>L66: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ doned the same and departed this Province, and has re-</t>
-        </is>
-      </c>
+      <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
@@ -966,7 +950,7 @@
       <c r="P8" s="1" t="inlineStr"/>
       <c r="Q8" s="1" t="inlineStr">
         <is>
-          <t>L90: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: the -----â€” day of -------your orator entered into vendee.</t>
+          <t>L90: punctuation artifact: double/multiple hyphen :: the -----— day of -------your orator entered into vendee.</t>
         </is>
       </c>
       <c r="R8" s="1" t="inlineStr"/>
@@ -1001,11 +985,7 @@
       <c r="H9" s="1" t="inlineStr"/>
       <c r="I9" s="1" t="inlineStr"/>
       <c r="J9" s="1" t="inlineStr"/>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>L69: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: Â£â€” which he paid on the â€” --------day of ------</t>
-        </is>
-      </c>
+      <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
@@ -1037,12 +1017,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1052,11 +1032,7 @@
       <c r="H10" s="1" t="inlineStr"/>
       <c r="I10" s="1" t="inlineStr"/>
       <c r="J10" s="1" t="inlineStr"/>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>L90: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: the -----â€” day of -------your orator entered into vendee.</t>
-        </is>
-      </c>
+      <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr"/>
@@ -1085,7 +1061,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1095,11 +1071,7 @@
       <c r="H11" s="1" t="inlineStr"/>
       <c r="I11" s="1" t="inlineStr"/>
       <c r="J11" s="1" t="inlineStr"/>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>L94: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: â€”</t>
-        </is>
-      </c>
+      <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr"/>
@@ -1128,7 +1100,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1206,7 +1178,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
